--- a/data/trans_camb/IMC_inf_MED_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 5,25</t>
+          <t>-26,55; 2,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-31,98; -0,86</t>
+          <t>-32,38; -1,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 11,35</t>
+          <t>-17,6; 11,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-40,58; -10,8</t>
+          <t>-38,51; -8,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,44; 4,36</t>
+          <t>-16,73; 3,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,96; -11,08</t>
+          <t>-31,28; -10,25</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-48,68; 14,54</t>
+          <t>-50,02; 7,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,72; -0,72</t>
+          <t>-62,06; -4,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,2; 25,78</t>
+          <t>-31,5; 27,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-71,41; -23,53</t>
+          <t>-69,38; -19,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-32,18; 10,06</t>
+          <t>-31,64; 8,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,02; -23,26</t>
+          <t>-60,03; -23,56</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-31,72; -6,74</t>
+          <t>-33,6; -8,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-30,84; -2,59</t>
+          <t>-31,66; -2,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,0; -5,6</t>
+          <t>-32,07; -6,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 1,73</t>
+          <t>-30,09; 2,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,9; -9,52</t>
+          <t>-27,56; -8,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,55; -3,61</t>
+          <t>-26,85; -3,67</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-67,11; -20,27</t>
+          <t>-69,69; -23,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-66,19; -6,96</t>
+          <t>-68,01; -5,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,5; -11,21</t>
+          <t>-50,49; -11,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,01; 3,49</t>
+          <t>-50,42; 3,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,54; -22,17</t>
+          <t>-52,26; -19,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -7,75</t>
+          <t>-52,09; -8,17</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 10,47</t>
+          <t>-18,79; 10,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 7,34</t>
+          <t>-30,49; 6,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 2,37</t>
+          <t>-28,63; 1,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,68; 4,04</t>
+          <t>-32,71; 4,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,12; 3,62</t>
+          <t>-18,35; 2,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,0; 5,83</t>
+          <t>-25,5; 3,87</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,31; 37,82</t>
+          <t>-46,82; 37,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,54; 24,75</t>
+          <t>-76,5; 25,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-42,39; 5,67</t>
+          <t>-43,26; 3,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 7,79</t>
+          <t>-52,32; 9,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-34,51; 9,16</t>
+          <t>-35,04; 6,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 14,57</t>
+          <t>-50,59; 8,48</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,54; 3,19</t>
+          <t>-16,85; 2,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-38,62; -6,92</t>
+          <t>-38,02; -6,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,85; -1,28</t>
+          <t>-21,91; -2,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-23,62; 1,65</t>
+          <t>-24,46; 1,57</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-15,58; -2,41</t>
+          <t>-16,32; -3,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,32; -6,98</t>
+          <t>-31,05; -6,59</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 7,08</t>
+          <t>-32,78; 5,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,95; -16,54</t>
+          <t>-76,57; -15,39</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,98; -3,22</t>
+          <t>-35,87; -4,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,74; 3,57</t>
+          <t>-42,12; 2,94</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,16; -5,36</t>
+          <t>-29,74; -6,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,03; -14,38</t>
+          <t>-57,58; -13,13</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,41; -2,85</t>
+          <t>-24,52; -2,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 16,91</t>
+          <t>-17,47; 17,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 10,04</t>
+          <t>-12,75; 10,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,24; 14,4</t>
+          <t>-15,95; 13,18</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,58; 0,44</t>
+          <t>-16,14; 0,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 10,64</t>
+          <t>-12,05; 9,84</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,85; -6,47</t>
+          <t>-45,48; -6,86</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,07; 38,5</t>
+          <t>-32,62; 40,23</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 22,49</t>
+          <t>-23,53; 22,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,69; 32,3</t>
+          <t>-29,32; 30,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 0,9</t>
+          <t>-29,49; 0,93</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 22,51</t>
+          <t>-23,6; 21,37</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 4,76</t>
+          <t>-28,38; 8,21</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-52,41; -17,89</t>
+          <t>-53,44; -18,52</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 11,36</t>
+          <t>-21,82; 10,15</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 7,9</t>
+          <t>-31,04; 7,62</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,98; 4,06</t>
+          <t>-20,49; 4,52</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-35,12; -7,58</t>
+          <t>-35,55; -8,99</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-48,82; 10,47</t>
+          <t>-48,67; 20,96</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-89,36; -38,53</t>
+          <t>-91,44; -40,16</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-38,15; 24,47</t>
+          <t>-35,44; 23,3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-51,52; 16,23</t>
+          <t>-51,32; 15,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,63; 9,61</t>
+          <t>-35,07; 9,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-61,41; -14,65</t>
+          <t>-62,19; -17,22</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-16,24; -6,07</t>
+          <t>-16,48; -5,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-28,37; -10,99</t>
+          <t>-26,72; -10,24</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -3,85</t>
+          <t>-14,08; -3,99</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-19,73; -6,44</t>
+          <t>-19,81; -6,81</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,56; -6,38</t>
+          <t>-13,65; -6,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-21,89; -10,49</t>
+          <t>-20,77; -9,59</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,51; -13,9</t>
+          <t>-34,2; -13,47</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,83; -24,76</t>
+          <t>-56,62; -23,18</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-25,74; -7,06</t>
+          <t>-25,13; -7,67</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-35,07; -11,72</t>
+          <t>-35,41; -12,89</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,49; -13,39</t>
+          <t>-26,02; -13,11</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-42,88; -21,31</t>
+          <t>-41,04; -20,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Clase-trans_camb.xlsx
@@ -513,7 +513,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad observado</t>
+          <t>Menores con sobrepeso u obesidad (IMC recogido por medición)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,55; 2,57</t>
+          <t>-26,11; 4,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-32,38; -1,84</t>
+          <t>-32,2; -0,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-17,6; 11,35</t>
+          <t>-18,26; 11,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-38,51; -8,36</t>
+          <t>-38,47; -9,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 3,57</t>
+          <t>-16,57; 4,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-31,28; -10,25</t>
+          <t>-32,06; -10,89</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-50,02; 7,79</t>
+          <t>-49,19; 10,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,06; -4,48</t>
+          <t>-60,73; -1,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 27,97</t>
+          <t>-31,03; 27,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-69,38; -19,66</t>
+          <t>-70,18; -22,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,64; 8,97</t>
+          <t>-31,6; 10,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,03; -23,56</t>
+          <t>-60,61; -23,08</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-33,6; -8,67</t>
+          <t>-31,6; -8,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,66; -2,52</t>
+          <t>-31,52; -2,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,07; -6,5</t>
+          <t>-31,3; -6,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 2,06</t>
+          <t>-29,44; 3,57</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,56; -8,58</t>
+          <t>-27,93; -10,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,85; -3,67</t>
+          <t>-26,45; -4,64</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,69; -23,25</t>
+          <t>-68,03; -22,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,01; -5,91</t>
+          <t>-68,21; -6,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,49; -11,88</t>
+          <t>-50,93; -14,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,42; 3,52</t>
+          <t>-50,51; 6,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,26; -19,72</t>
+          <t>-53,29; -23,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,09; -8,17</t>
+          <t>-50,7; -10,07</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 10,57</t>
+          <t>-19,38; 9,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,49; 6,85</t>
+          <t>-30,93; 4,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-28,63; 1,98</t>
+          <t>-26,48; 1,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 4,71</t>
+          <t>-33,79; 5,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,35; 2,74</t>
+          <t>-18,78; 3,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,5; 3,87</t>
+          <t>-26,66; 2,91</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-46,82; 37,12</t>
+          <t>-47,42; 29,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,5; 25,58</t>
+          <t>-76,18; 17,62</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 3,97</t>
+          <t>-40,45; 3,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 9,61</t>
+          <t>-53,91; 11,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,04; 6,87</t>
+          <t>-36,12; 7,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-50,59; 8,48</t>
+          <t>-51,73; 7,34</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,85; 2,02</t>
+          <t>-16,0; 3,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-38,02; -6,41</t>
+          <t>-42,04; -7,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-21,91; -2,27</t>
+          <t>-20,69; -1,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 1,57</t>
+          <t>-22,99; 3,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,32; -3,1</t>
+          <t>-16,41; -2,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-31,05; -6,59</t>
+          <t>-32,81; -7,36</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 5,1</t>
+          <t>-30,97; 7,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-76,57; -15,39</t>
+          <t>-79,92; -15,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-35,87; -4,49</t>
+          <t>-34,57; -3,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,12; 2,94</t>
+          <t>-39,61; 6,96</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,74; -6,6</t>
+          <t>-29,69; -6,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,58; -13,13</t>
+          <t>-60,35; -14,6</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-24,52; -2,85</t>
+          <t>-25,1; -2,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 17,45</t>
+          <t>-16,94; 18,25</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,75; 10,21</t>
+          <t>-11,99; 10,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 13,18</t>
+          <t>-15,6; 13,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 0,34</t>
+          <t>-15,91; 0,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 9,84</t>
+          <t>-12,22; 9,2</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,48; -6,86</t>
+          <t>-45,02; -5,84</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 40,23</t>
+          <t>-31,38; 38,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,53; 22,93</t>
+          <t>-23,07; 24,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-29,32; 30,31</t>
+          <t>-28,95; 30,65</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,49; 0,93</t>
+          <t>-29,57; 1,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 21,37</t>
+          <t>-22,74; 20,44</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 8,21</t>
+          <t>-29,08; 6,52</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-53,44; -18,52</t>
+          <t>-53,45; -16,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-21,82; 10,15</t>
+          <t>-22,25; 10,88</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 7,62</t>
+          <t>-28,86; 6,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 4,52</t>
+          <t>-20,02; 2,51</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-35,55; -8,99</t>
+          <t>-35,69; -7,02</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-48,67; 20,96</t>
+          <t>-49,12; 16,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-91,44; -40,16</t>
+          <t>-91,33; -33,12</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,44; 23,3</t>
+          <t>-35,66; 23,19</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-51,32; 15,45</t>
+          <t>-51,9; 14,56</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-35,07; 9,47</t>
+          <t>-33,59; 6,09</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-62,19; -17,22</t>
+          <t>-62,28; -14,31</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-16,48; -5,81</t>
+          <t>-16,43; -5,94</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-26,72; -10,24</t>
+          <t>-27,23; -10,11</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -3,99</t>
+          <t>-14,36; -3,45</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-19,81; -6,81</t>
+          <t>-19,48; -6,44</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,65; -6,23</t>
+          <t>-13,68; -6,05</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-20,77; -9,59</t>
+          <t>-20,6; -9,6</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-34,2; -13,47</t>
+          <t>-33,85; -13,5</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-56,62; -23,18</t>
+          <t>-58,07; -22,97</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-25,13; -7,67</t>
+          <t>-25,27; -6,72</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-35,41; -12,89</t>
+          <t>-35,03; -12,2</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,02; -13,11</t>
+          <t>-26,55; -12,74</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-41,04; -20,06</t>
+          <t>-40,4; -19,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-24,98</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-11,69</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-16,85</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-3,11</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-24,73</t>
+          <t>-16,52</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-21,16</t>
+          <t>-21,08</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-26,11; 4,04</t>
+          <t>-17,0; 11,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-32,2; -0,5</t>
+          <t>-40,73; -10,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 11,65</t>
+          <t>-25,47; 5,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-38,47; -9,85</t>
+          <t>-31,79; -0,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 4,53</t>
+          <t>-16,44; 4,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,06; -10,89</t>
+          <t>-31,53; -10,29</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-6,29%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-50,45%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-24,91%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-35,91%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-6,29%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-49,95%</t>
+          <t>-35,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-43,97%</t>
+          <t>-43,81%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 10,63</t>
+          <t>-30,2; 25,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,73; -1,34</t>
+          <t>-72,55; -23,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 27,88</t>
+          <t>-48,68; 14,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-70,18; -22,62</t>
+          <t>-61,73; 1,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,6; 10,71</t>
+          <t>-32,18; 10,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,61; -23,08</t>
+          <t>-60,49; -23,78</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-18,86</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-13,1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-20,21</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-17,8</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-18,86</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-14,27</t>
+          <t>-18,02</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-15,53</t>
+          <t>-15,25</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-31,6; -8,17</t>
+          <t>-31,0; -5,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-31,52; -2,39</t>
+          <t>-31,04; 3,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,3; -6,42</t>
+          <t>-31,72; -6,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-29,44; 3,57</t>
+          <t>-31,34; -2,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,93; -10,25</t>
+          <t>-27,9; -9,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,45; -4,64</t>
+          <t>-26,38; -3,31</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-33,73%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-23,44%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-49,73%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-43,81%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-33,73%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-25,52%</t>
+          <t>-44,34%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-32,25%</t>
+          <t>-31,66%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-68,03; -22,45</t>
+          <t>-49,5; -11,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,21; -6,09</t>
+          <t>-49,09; 7,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,93; -14,37</t>
+          <t>-67,11; -20,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,51; 6,22</t>
+          <t>-66,92; -7,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-53,29; -23,51</t>
+          <t>-52,54; -22,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,7; -10,07</t>
+          <t>-51,32; -7,31</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-12,62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-12,83</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-4,99</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-13,99</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-12,62</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-14,84</t>
+          <t>-12,88</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-10,82</t>
+          <t>-10,02</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-19,38; 9,01</t>
+          <t>-27,78; 2,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-30,93; 4,56</t>
+          <t>-30,85; 5,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 1,79</t>
+          <t>-19,38; 10,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-33,79; 5,85</t>
+          <t>-30,64; 8,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-18,78; 3,02</t>
+          <t>-18,12; 3,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,66; 2,91</t>
+          <t>-23,49; 5,94</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-21,33%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-21,7%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-13,9%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-38,99%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-21,33%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-25,08%</t>
+          <t>-35,89%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-22,8%</t>
+          <t>-21,11%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 29,73</t>
+          <t>-42,39; 5,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,18; 17,62</t>
+          <t>-48,39; 10,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 3,8</t>
+          <t>-47,31; 37,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,91; 11,36</t>
+          <t>-77,18; 28,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,12; 7,62</t>
+          <t>-34,51; 9,16</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,73; 7,34</t>
+          <t>-44,98; 14,53</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-11,4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-12,64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-6,79</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-21,01</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-11,4</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-11,28</t>
+          <t>-18,61</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-17,4</t>
+          <t>-15,76</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 3,09</t>
+          <t>-19,85; -1,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-42,04; -7,35</t>
+          <t>-24,8; 0,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -1,65</t>
+          <t>-16,54; 3,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 3,31</t>
+          <t>-28,62; -7,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-16,41; -2,96</t>
+          <t>-15,58; -2,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-32,81; -7,36</t>
+          <t>-24,56; -7,13</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-20,41%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-22,63%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-14,5%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-44,87%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-20,41%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-20,2%</t>
+          <t>-39,75%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-33,64%</t>
+          <t>-30,47%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 7,11</t>
+          <t>-33,98; -3,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-79,92; -15,62</t>
+          <t>-42,24; 2,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,57; -3,5</t>
+          <t>-31,71; 7,08</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-39,61; 6,96</t>
+          <t>-57,38; -18,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-29,69; -6,79</t>
+          <t>-29,16; -5,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,35; -14,6</t>
+          <t>-44,92; -13,85</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,45</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-2,41</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-14,18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>-0,52</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,89</t>
+          <t>-3,58</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,49</t>
+          <t>-3,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,1; -2,88</t>
+          <t>-13,91; 10,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 18,25</t>
+          <t>-15,58; 13,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 10,35</t>
+          <t>-25,41; -2,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 13,17</t>
+          <t>-18,68; 12,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-15,91; 0,74</t>
+          <t>-16,58; 0,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 9,2</t>
+          <t>-13,17; 8,0</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-2,95%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-4,9%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-28,28%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>-1,04%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-2,95%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-3,85%</t>
+          <t>-7,13%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-3,01%</t>
+          <t>-6,05%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-45,02; -5,84</t>
+          <t>-24,84; 22,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,38; 38,3</t>
+          <t>-29,8; 31,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,07; 24,48</t>
+          <t>-46,85; -6,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-28,95; 30,65</t>
+          <t>-34,88; 25,92</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-29,57; 1,83</t>
+          <t>-30,94; 0,9</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-22,74; 20,44</t>
+          <t>-25,07; 17,53</t>
         </is>
       </c>
     </row>
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-5,36</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-9,58</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-11,55</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-36,84</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-5,36</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-11,9</t>
+          <t>-37,68</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-22,23</t>
+          <t>-22,1</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 6,52</t>
+          <t>-22,92; 11,36</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-53,45; -16,57</t>
+          <t>-28,34; 10,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-22,25; 10,88</t>
+          <t>-27,41; 4,76</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 6,86</t>
+          <t>-53,08; -18,86</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 2,51</t>
+          <t>-20,98; 4,06</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-35,69; -7,02</t>
+          <t>-35,75; -6,96</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-9,88%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-17,67%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-22,68%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-72,3%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-9,88%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-21,95%</t>
+          <t>-73,97%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-42,1%</t>
+          <t>-41,85%</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-49,12; 16,16</t>
+          <t>-38,15; 24,47</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-91,33; -33,12</t>
+          <t>-47,18; 22,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,66; 23,19</t>
+          <t>-48,82; 10,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-51,9; 14,56</t>
+          <t>-89,61; -39,72</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-33,59; 6,09</t>
+          <t>-35,63; 9,61</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-62,28; -14,31</t>
+          <t>-62,14; -14,29</t>
         </is>
       </c>
     </row>
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-9,2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-13,19</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-10,94</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-17,7</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-9,2</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-13,2</t>
+          <t>-17,43</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-14,97</t>
+          <t>-14,69</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-16,43; -5,94</t>
+          <t>-14,67; -3,85</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-27,23; -10,11</t>
+          <t>-19,82; -6,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -3,45</t>
+          <t>-16,24; -6,07</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -6,44</t>
+          <t>-23,69; -10,88</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-13,68; -6,05</t>
+          <t>-13,56; -6,38</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-20,6; -9,6</t>
+          <t>-19,39; -9,96</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-17,03%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-24,42%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-23,99%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-38,79%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-17,03%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-24,45%</t>
+          <t>-38,21%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-30,01%</t>
+          <t>-29,45%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,85; -13,5</t>
+          <t>-25,74; -7,06</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-58,07; -22,97</t>
+          <t>-35,36; -12,24</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -6,72</t>
+          <t>-33,51; -13,9</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-35,03; -12,2</t>
+          <t>-49,87; -25,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-26,55; -12,74</t>
+          <t>-26,49; -13,39</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-40,4; -19,91</t>
+          <t>-37,88; -20,49</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IMC_inf_MED_R2-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R2-Clase-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-3.112394330651791</v>
+        <v>-4.172371642331274</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-24.97809139580938</v>
+        <v>-21.19503422923252</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-11.68813521337863</v>
+        <v>-10.44439624211854</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-16.51863890897061</v>
+        <v>-16.04383303493722</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-6.756353052684222</v>
+        <v>-6.834147463073164</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-21.08414392469709</v>
+        <v>-18.88359001779268</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-17.00149187618745</v>
+        <v>-17.73194652745559</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-40.72820012766144</v>
+        <v>-35.71249693096829</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-25.46931094988799</v>
+        <v>-23.65207482015103</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-31.79237916384375</v>
+        <v>-31.73370658836275</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-16.43828617020757</v>
+        <v>-16.16486685310106</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-31.525127251784</v>
+        <v>-28.7655714008641</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>11.3504308845898</v>
+        <v>8.669962412424608</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-10.71015235193287</v>
+        <v>-6.469037623108827</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5.249565355912193</v>
+        <v>3.203872824303546</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.9757399906633771</v>
+        <v>-0.1431809580573027</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4.357760850657581</v>
+        <v>3.088644103040548</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-10.29020040185268</v>
+        <v>-7.95104406701105</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-0.06286542798440126</v>
+        <v>-0.08837069756146303</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.5045178210121617</v>
+        <v>-0.4489101451734129</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.2490767464263504</v>
+        <v>-0.2280263128502913</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.3520158485271996</v>
+        <v>-0.3502754976098418</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.1404019312167707</v>
+        <v>-0.1470496832921609</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.4381438480192712</v>
+        <v>-0.4063163615563468</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.3019692992469368</v>
+        <v>-0.3213525369610942</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.7255165349698807</v>
+        <v>-0.6726687248627518</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.4868480383163337</v>
+        <v>-0.4551988222729327</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.6172964684511052</v>
+        <v>-0.6159669998651747</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.3217662327419132</v>
+        <v>-0.318558695121903</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.6048506845743162</v>
+        <v>-0.5717233511751539</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.2577588478339924</v>
+        <v>0.2212664640681275</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>-0.2333381566177458</v>
+        <v>-0.1422241117492279</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.1453550884021935</v>
+        <v>0.08928095906618209</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.01855784731904863</v>
+        <v>0.02676549179519587</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.1005931709297719</v>
+        <v>0.07457033543379102</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.2378420938563074</v>
+        <v>-0.1910701165141704</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-18.8577693202762</v>
+        <v>-17.49076127347947</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-13.10056009568487</v>
+        <v>-13.81984459495002</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-20.20628782762362</v>
+        <v>-18.39864691721082</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-18.01580829967016</v>
+        <v>-17.70535820239046</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-18.7428145375845</v>
+        <v>-17.49143990352711</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-15.25014147822723</v>
+        <v>-15.9626337430195</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-31.0005404723521</v>
+        <v>-29.30813709228353</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-31.04297889288316</v>
+        <v>-31.16362181874734</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-31.72084126849582</v>
+        <v>-30.91144509426032</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-31.33981370533255</v>
+        <v>-30.51022098758531</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-27.89595638752225</v>
+        <v>-25.38157145135973</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-26.3801957357976</v>
+        <v>-27.49739603704919</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-5.595765043514972</v>
+        <v>-5.592414377216326</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>3.66359325981259</v>
+        <v>2.511932296584615</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-6.740482195003046</v>
+        <v>-6.841446713644594</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-2.634313114671317</v>
+        <v>-2.676596516481368</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-9.517618720663066</v>
+        <v>-8.779945191879728</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-3.312219636340668</v>
+        <v>-5.165513055638863</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.3373481136158004</v>
+        <v>-0.3124950926605664</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.2343569464940824</v>
+        <v>-0.2469094140460144</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.4972994146267075</v>
+        <v>-0.4735934323679022</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.4433892557545842</v>
+        <v>-0.4557477188460796</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.389103123193094</v>
+        <v>-0.3678019505866029</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.3165948031132522</v>
+        <v>-0.3356549180378342</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.4949828240587788</v>
+        <v>-0.4785201067426026</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.490886439629581</v>
+        <v>-0.5279030274067827</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.6710803683365922</v>
+        <v>-0.6608562974282294</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.6691577282498483</v>
+        <v>-0.6897605748135952</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.5253968078348608</v>
+        <v>-0.4948957012664777</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.5131807672540754</v>
+        <v>-0.5352222308065417</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-0.1120615546207808</v>
+        <v>-0.1169962387771397</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.07768601326615736</v>
+        <v>0.0470077382751844</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-0.2027483688801113</v>
+        <v>-0.2097896691227275</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.07348598891612942</v>
+        <v>-0.05727155265788698</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.2217369518673611</v>
+        <v>-0.203786398654078</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.0730563986731793</v>
+        <v>-0.115327403565678</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-12.61564173136724</v>
+        <v>-9.079548409519239</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-12.83410003202009</v>
+        <v>-13.68927105606235</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-4.987432540547221</v>
+        <v>-6.117728265527367</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-12.88224284203922</v>
+        <v>-11.86178168620428</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-7.863509720180556</v>
+        <v>-6.387669423385944</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-10.01816190614882</v>
+        <v>-10.5429965121174</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-27.77589988366302</v>
+        <v>-22.00189749707613</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-30.84500056936582</v>
+        <v>-30.70720214143358</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-19.38009607575882</v>
+        <v>-19.1137446980697</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-30.63915690428732</v>
+        <v>-28.06076676870745</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-18.11504360321514</v>
+        <v>-16.32023346496985</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-23.48944014354156</v>
+        <v>-22.81386793849208</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>2.370488034256102</v>
+        <v>4.875930976631361</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>5.913566993668972</v>
+        <v>5.365272418544093</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>10.46589508705784</v>
+        <v>7.437606352207082</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>8.11849349068555</v>
+        <v>8.030907705407321</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>3.619747430921047</v>
+        <v>3.261844496024323</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>5.941372865238519</v>
+        <v>3.99696724289989</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-0.2132837873857074</v>
+        <v>-0.1580226566601465</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.2169771083234157</v>
+        <v>-0.2382513845899924</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.1389623443916793</v>
+        <v>-0.1677852599977431</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.3589315046968603</v>
+        <v>-0.3253220865449291</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.1657227717467426</v>
+        <v>-0.1369267178847954</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.2111318759654932</v>
+        <v>-0.2260007231729683</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.4238932048565149</v>
+        <v>-0.3482140386936342</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.4839388186716935</v>
+        <v>-0.5006845265402351</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.4730615592935693</v>
+        <v>-0.458001909602291</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.7717731118460623</v>
+        <v>-0.7059563634683226</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.34505823439845</v>
+        <v>-0.3147124758295193</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.449775160420306</v>
+        <v>-0.4688378452906158</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.05674485924226524</v>
+        <v>0.09431052602697479</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.1023395039699459</v>
+        <v>0.09385529917597964</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.3781883165871077</v>
+        <v>0.2518025982050729</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.288570986503868</v>
+        <v>0.3610173377391878</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.09156185194050789</v>
+        <v>0.0756019548037298</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.1453324210099078</v>
+        <v>0.08624421822927729</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-11.39820735048535</v>
+        <v>-6.788757220342462</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-12.63901544160198</v>
+        <v>-9.667563843589717</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-6.788529969574464</v>
+        <v>-6.267979286958431</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-18.61385313439025</v>
+        <v>-15.90273894141418</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-9.510318927295025</v>
+        <v>-6.800109020065609</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-15.75570538137717</v>
+        <v>-12.71815317325091</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-19.85082536200105</v>
+        <v>-14.49501829224104</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-24.79986997329697</v>
+        <v>-22.68198640369602</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-16.53816954720353</v>
+        <v>-15.49003623731723</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-28.62164453966086</v>
+        <v>-26.66245123793374</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-15.58065136658816</v>
+        <v>-12.79816629011385</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-24.56162928208762</v>
+        <v>-20.76888158958314</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>-1.275425960648055</v>
+        <v>2.683024590496224</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.8046097164622343</v>
+        <v>2.860194627241649</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3.190849435445996</v>
+        <v>2.05359801848157</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-7.793612063985771</v>
+        <v>-6.239377059581911</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-2.407291298529326</v>
+        <v>-0.6673377347504104</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-7.127947689346674</v>
+        <v>-4.325398858873244</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.2040971226111281</v>
+        <v>-0.1278313249949206</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.2263151217510302</v>
+        <v>-0.1820388409083098</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-0.1449553270619661</v>
+        <v>-0.1410328964620269</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.3974611854218676</v>
+        <v>-0.3578201573278403</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.1839101606240717</v>
+        <v>-0.1385914530617442</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.3046831898684587</v>
+        <v>-0.2592057455757776</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.339782185234206</v>
+        <v>-0.259483673316083</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.4223603462521197</v>
+        <v>-0.4039400612874592</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.3170982189893239</v>
+        <v>-0.3078836003232236</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.573843693908445</v>
+        <v>-0.5552282009752206</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.2916003062175475</v>
+        <v>-0.2454847533978733</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.4492460162056835</v>
+        <v>-0.404036851944889</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>-0.03217094047685373</v>
+        <v>0.05402098147467713</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>0.02540165308218329</v>
+        <v>0.05976178001566999</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>0.07081460682311128</v>
+        <v>0.05087865955528537</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.1838750866134287</v>
+        <v>-0.1433902560104912</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.05362357816495352</v>
+        <v>-0.01389328209575441</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.1385201957702297</v>
+        <v>-0.08896571073311732</v>
       </c>
     </row>
     <row r="28">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-1.450821540842279</v>
+        <v>-4.48326967160636</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-2.40690167469752</v>
+        <v>-1.770703926821471</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-14.18060585114442</v>
+        <v>-15.45885088067336</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-3.575953843251617</v>
+        <v>-0.955614096986912</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-7.731794800772057</v>
+        <v>-9.966784687636626</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-3.002735691857872</v>
+        <v>-1.872992257696343</v>
       </c>
     </row>
     <row r="29">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-13.91275577643103</v>
+        <v>-15.92973912046219</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-15.58440667210593</v>
+        <v>-15.12089075328936</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-25.40926726747809</v>
+        <v>-26.45956951004361</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-18.68048971228172</v>
+        <v>-15.81221282813553</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-16.58156875565688</v>
+        <v>-17.33943578417227</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-13.16929385346025</v>
+        <v>-11.58232353358543</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>10.03924903684473</v>
+        <v>6.659151788236479</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>13.21730801609483</v>
+        <v>13.012084862908</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-2.853533333910394</v>
+        <v>-5.114044979195656</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>12.31174369254823</v>
+        <v>12.71592478345664</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.4363230082467005</v>
+        <v>-2.694149936927343</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>8.000528703604367</v>
+        <v>8.081795765917848</v>
       </c>
     </row>
     <row r="31">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.0295475169697083</v>
+        <v>-0.09288541348126145</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.04901910129915535</v>
+        <v>-0.03668585172053122</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-0.2827867880904364</v>
+        <v>-0.2974390938688896</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.07131095189499023</v>
+        <v>-0.01838668302645167</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.1557307926681273</v>
+        <v>-0.1986686447868244</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.06047993014755255</v>
+        <v>-0.03733449103142836</v>
       </c>
     </row>
     <row r="32">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-0.2484046385534529</v>
+        <v>-0.2951395605847207</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-0.2979906131225002</v>
+        <v>-0.2926147152278191</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.4685113416422044</v>
+        <v>-0.4614153678937147</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.3487546586447182</v>
+        <v>-0.2873636366967391</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.3093799625749362</v>
+        <v>-0.3188492089880353</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.2506992655490889</v>
+        <v>-0.2219287767171285</v>
       </c>
     </row>
     <row r="33">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>0.2248597842765807</v>
+        <v>0.1544367167138085</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>0.3132295250405625</v>
+        <v>0.3028708970600592</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-0.06472215174815109</v>
+        <v>-0.1050399494830283</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.2592072147507714</v>
+        <v>0.2681392677040504</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.008977079022404218</v>
+        <v>-0.05310508947444774</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>0.1752820411991363</v>
+        <v>0.1712664334925517</v>
       </c>
     </row>
     <row r="34">
@@ -1401,22 +1401,22 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>-5.358623602086171</v>
+        <v>-5.277331432598248</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>-9.577750273708862</v>
+        <v>-8.838058373083513</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-11.55346076500984</v>
+        <v>-16.82572224502915</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>-37.68464567475085</v>
+        <v>-40.31364420266537</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-8.350672533239202</v>
+        <v>-10.52493122364202</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>-22.09881113125799</v>
+        <v>-22.81016632740719</v>
       </c>
     </row>
     <row r="35">
@@ -1427,22 +1427,22 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>-22.91823406067022</v>
+        <v>-19.37434500331003</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>-28.3374563137166</v>
+        <v>-28.32772712324968</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-27.41088015059174</v>
+        <v>-33.27892279605038</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-53.08149497800603</v>
+        <v>-54.12354943873189</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-20.98175096003342</v>
+        <v>-22.89552779834137</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-35.75372995631513</v>
+        <v>-35.50578699714866</v>
       </c>
     </row>
     <row r="36">
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>11.35706773559064</v>
+        <v>10.44136442943023</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>10.10510634900534</v>
+        <v>10.15444709646927</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>4.758695275551113</v>
+        <v>-0.7705490946673536</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-18.86028597812088</v>
+        <v>-19.39249947619148</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>4.061456760642906</v>
+        <v>0.3420656717362792</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>-6.960625493100917</v>
+        <v>-8.96956639163181</v>
       </c>
     </row>
     <row r="37">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>-0.09884447252881676</v>
+        <v>-0.09869154084741698</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>-0.1766699331986891</v>
+        <v>-0.1652808071805311</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>-0.2267674575958336</v>
+        <v>-0.3140445925828951</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>-0.7396616013051223</v>
+        <v>-0.7524361679569554</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>-0.1581409148582146</v>
+        <v>-0.1966665993033355</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>-0.4184963780660241</v>
+        <v>-0.4262258579968472</v>
       </c>
     </row>
     <row r="38">
@@ -1505,22 +1505,22 @@
         </is>
       </c>
       <c r="C38" s="6" t="n">
-        <v>-0.3815185231944098</v>
+        <v>-0.3220072875822508</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>-0.4717983799809506</v>
+        <v>-0.4781394211211508</v>
       </c>
       <c r="E38" s="6" t="n">
-        <v>-0.4882322309885428</v>
+        <v>-0.5467390535100056</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>-0.8960971206395376</v>
+        <v>-0.896391146683903</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>-0.3562653087080049</v>
+        <v>-0.3830324490702605</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>-0.621434281464241</v>
+        <v>-0.6309805970622293</v>
       </c>
     </row>
     <row r="39">
@@ -1531,22 +1531,22 @@
         </is>
       </c>
       <c r="C39" s="6" t="n">
-        <v>0.2447471011081744</v>
+        <v>0.2214745229071488</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>0.2256119313593602</v>
+        <v>0.2221339123134042</v>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.1047331248446054</v>
+        <v>0.003292631586221108</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>-0.3971979745011915</v>
+        <v>-0.4020563558398939</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.09608219047538498</v>
+        <v>0.007807445803900644</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>-0.142930175174885</v>
+        <v>-0.1699087556618524</v>
       </c>
     </row>
     <row r="40">
@@ -1561,22 +1561,22 @@
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>-9.198335086817622</v>
+        <v>-7.794107292492275</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>-13.18974553721578</v>
+        <v>-11.52140519742298</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-10.94459421098312</v>
+        <v>-11.38045580205065</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-17.43245667770236</v>
+        <v>-16.3387229575184</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-9.926199090032611</v>
+        <v>-9.414958190231076</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>-14.68957757912865</v>
+        <v>-13.37404064420041</v>
       </c>
     </row>
     <row r="41">
@@ -1587,22 +1587,22 @@
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>-14.67491578211102</v>
+        <v>-13.21836739102718</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>-19.82072700564708</v>
+        <v>-17.76219686741424</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-16.23964455302137</v>
+        <v>-16.06630524393003</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-23.69404242010548</v>
+        <v>-21.77665790504857</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-13.55654185548701</v>
+        <v>-13.03284488216998</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>-19.39487811557243</v>
+        <v>-17.62484121267519</v>
       </c>
     </row>
     <row r="42">
@@ -1613,22 +1613,22 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>-3.853375696031223</v>
+        <v>-3.27655122025986</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>-6.446041843967469</v>
+        <v>-4.461358717212302</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-6.074247490790807</v>
+        <v>-6.3982756608954</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-10.87962510081391</v>
+        <v>-10.12352343018494</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-6.380106215216641</v>
+        <v>-6.078282835248435</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>-9.962649165414662</v>
+        <v>-8.752987542406419</v>
       </c>
     </row>
     <row r="43">
@@ -1639,22 +1639,22 @@
         </is>
       </c>
       <c r="C43" s="6" t="n">
-        <v>-0.1703241559266042</v>
+        <v>-0.1489386637712535</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>-0.2442324892830375</v>
+        <v>-0.2201641099455078</v>
       </c>
       <c r="E43" s="6" t="n">
-        <v>-0.2398762398851408</v>
+        <v>-0.251192376491677</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>-0.3820728369820695</v>
+        <v>-0.3606325370376323</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>-0.1989983016488778</v>
+        <v>-0.1925400719500556</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>-0.2944934877561912</v>
+        <v>-0.2735050645863904</v>
       </c>
     </row>
     <row r="44">
@@ -1665,22 +1665,22 @@
         </is>
       </c>
       <c r="C44" s="6" t="n">
-        <v>-0.2573665396829937</v>
+        <v>-0.2402508073412246</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>-0.3535686175482334</v>
+        <v>-0.3292696206303832</v>
       </c>
       <c r="E44" s="6" t="n">
-        <v>-0.335064112869887</v>
+        <v>-0.3377820407703637</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>-0.4987196769994432</v>
+        <v>-0.4629826893851017</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>-0.2648664522519902</v>
+        <v>-0.2569343326023679</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>-0.3787938930910846</v>
+        <v>-0.3514743025233375</v>
       </c>
     </row>
     <row r="45">
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="C45" s="6" t="n">
-        <v>-0.070577834902792</v>
+        <v>-0.06569694624198734</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>-0.1224256719237042</v>
+        <v>-0.09098109314563382</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>-0.1390092591358519</v>
+        <v>-0.1485308775270188</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>-0.2519435646412904</v>
+        <v>-0.2314579778289835</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>-0.1338890748587745</v>
+        <v>-0.1283854037373274</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>-0.2049448773065467</v>
+        <v>-0.1882546094710427</v>
       </c>
     </row>
     <row r="46">
